--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/131.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/131.xlsx
@@ -426,13 +426,13 @@
         <v>-16.16183234146336</v>
       </c>
       <c r="E2">
-        <v>-23.81118937033514</v>
+        <v>-32.25737077507633</v>
       </c>
       <c r="F2">
-        <v>-4.207254163411515</v>
+        <v>-6.201611641573938</v>
       </c>
       <c r="G2">
-        <v>-16.95145227626332</v>
+        <v>-21.5826815874074</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.7129079486785</v>
       </c>
       <c r="E3">
-        <v>-24.29057815726113</v>
+        <v>-32.38353179669303</v>
       </c>
       <c r="F3">
-        <v>-4.169621432302334</v>
+        <v>-5.785763750061961</v>
       </c>
       <c r="G3">
-        <v>-16.88031375224378</v>
+        <v>-21.30960028251183</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.18643231483044</v>
       </c>
       <c r="E4">
-        <v>-25.05262070632388</v>
+        <v>-31.5372007609255</v>
       </c>
       <c r="F4">
-        <v>-3.907333804819121</v>
+        <v>-6.208980797989242</v>
       </c>
       <c r="G4">
-        <v>-16.82979606511458</v>
+        <v>-21.38231707410146</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.60816026607849</v>
       </c>
       <c r="E5">
-        <v>-25.15602388181503</v>
+        <v>-32.22587523835298</v>
       </c>
       <c r="F5">
-        <v>-4.014639689810366</v>
+        <v>-6.492781126923159</v>
       </c>
       <c r="G5">
-        <v>-16.46283573018173</v>
+        <v>-21.00857609481604</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.99218873946645</v>
       </c>
       <c r="E6">
-        <v>-26.39181273919021</v>
+        <v>-33.33595139303824</v>
       </c>
       <c r="F6">
-        <v>-3.806302802904082</v>
+        <v>-6.069624549816282</v>
       </c>
       <c r="G6">
-        <v>-16.18148410634559</v>
+        <v>-20.93822014213842</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.35526251086219</v>
       </c>
       <c r="E7">
-        <v>-26.10089904046346</v>
+        <v>-35.25225668191609</v>
       </c>
       <c r="F7">
-        <v>-3.889233148700549</v>
+        <v>-6.057117858768815</v>
       </c>
       <c r="G7">
-        <v>-16.00187167879236</v>
+        <v>-20.61811893229601</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.69876996666503</v>
       </c>
       <c r="E8">
-        <v>-26.28300709420792</v>
+        <v>-34.56237763040257</v>
       </c>
       <c r="F8">
-        <v>-3.846420636221662</v>
+        <v>-5.914938534487113</v>
       </c>
       <c r="G8">
-        <v>-15.80400909692551</v>
+        <v>-21.30713936634225</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.02098516201022</v>
       </c>
       <c r="E9">
-        <v>-27.30669581448585</v>
+        <v>-35.17867350776545</v>
       </c>
       <c r="F9">
-        <v>-3.927910451104661</v>
+        <v>-5.763913074710915</v>
       </c>
       <c r="G9">
-        <v>-15.47208236458286</v>
+        <v>-20.58753466614043</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.33725888418236</v>
       </c>
       <c r="E10">
-        <v>-27.96200223118781</v>
+        <v>-35.14778478655914</v>
       </c>
       <c r="F10">
-        <v>-3.756179119728087</v>
+        <v>-5.771877827288833</v>
       </c>
       <c r="G10">
-        <v>-15.24624900953252</v>
+        <v>-20.1557341119714</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.65106348361811</v>
       </c>
       <c r="E11">
-        <v>-28.80025899779966</v>
+        <v>-35.85560791632805</v>
       </c>
       <c r="F11">
-        <v>-3.684561787551653</v>
+        <v>-5.801563201535556</v>
       </c>
       <c r="G11">
-        <v>-15.01569889849048</v>
+        <v>-20.10628774368135</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.961535977496718</v>
       </c>
       <c r="E12">
-        <v>-29.23630123152423</v>
+        <v>-37.0874207735245</v>
       </c>
       <c r="F12">
-        <v>-3.74693039767583</v>
+        <v>-5.766910107974244</v>
       </c>
       <c r="G12">
-        <v>-14.34586048568075</v>
+        <v>-20.1224083852029</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.267198231798343</v>
       </c>
       <c r="E13">
-        <v>-29.60949956720735</v>
+        <v>-36.84267939577996</v>
       </c>
       <c r="F13">
-        <v>-3.621994369250803</v>
+        <v>-5.689811468693486</v>
       </c>
       <c r="G13">
-        <v>-13.99031552055322</v>
+        <v>-19.44898031600714</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.590664445854214</v>
       </c>
       <c r="E14">
-        <v>-30.62526572220887</v>
+        <v>-37.61415702043769</v>
       </c>
       <c r="F14">
-        <v>-3.554392962243141</v>
+        <v>-5.631750369063866</v>
       </c>
       <c r="G14">
-        <v>-13.78200881046265</v>
+        <v>-18.52401380206436</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.940537391233399</v>
       </c>
       <c r="E15">
-        <v>-30.88743946064594</v>
+        <v>-37.83615866595272</v>
       </c>
       <c r="F15">
-        <v>-3.352243151468367</v>
+        <v>-5.250261500685206</v>
       </c>
       <c r="G15">
-        <v>-13.40570191591774</v>
+        <v>-19.68421929265764</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.321789228926973</v>
       </c>
       <c r="E16">
-        <v>-31.74180853777707</v>
+        <v>-38.75033077082915</v>
       </c>
       <c r="F16">
-        <v>-3.498995892180924</v>
+        <v>-5.260056116855908</v>
       </c>
       <c r="G16">
-        <v>-12.90752717143348</v>
+        <v>-18.45159232041507</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.73817372222791</v>
       </c>
       <c r="E17">
-        <v>-32.12636881474544</v>
+        <v>-38.99969798477253</v>
       </c>
       <c r="F17">
-        <v>-3.206535810418142</v>
+        <v>-5.343823113729202</v>
       </c>
       <c r="G17">
-        <v>-12.6516476705633</v>
+        <v>-18.67583264239831</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.203553841949153</v>
       </c>
       <c r="E18">
-        <v>-33.73372802139799</v>
+        <v>-39.7506503009905</v>
       </c>
       <c r="F18">
-        <v>-3.06968537363865</v>
+        <v>-5.169003628674992</v>
       </c>
       <c r="G18">
-        <v>-11.97387526402285</v>
+        <v>-18.45104271580387</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.716046186527938</v>
       </c>
       <c r="E19">
-        <v>-33.82348237623003</v>
+        <v>-39.54043853755444</v>
       </c>
       <c r="F19">
-        <v>-3.061099345508633</v>
+        <v>-5.20026455772184</v>
       </c>
       <c r="G19">
-        <v>-11.93303061805088</v>
+        <v>-17.84908621461594</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.267544265072397</v>
       </c>
       <c r="E20">
-        <v>-34.12389228495086</v>
+        <v>-40.51058031692867</v>
       </c>
       <c r="F20">
-        <v>-3.124059409958409</v>
+        <v>-5.089564851481325</v>
       </c>
       <c r="G20">
-        <v>-11.09837316508869</v>
+        <v>-17.55627984631577</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.852768187007261</v>
       </c>
       <c r="E21">
-        <v>-34.7225701341869</v>
+        <v>-40.92339147899389</v>
       </c>
       <c r="F21">
-        <v>-2.998487195368032</v>
+        <v>-4.8178346639736</v>
       </c>
       <c r="G21">
-        <v>-11.3248397959</v>
+        <v>-17.11156112286721</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.474179760960473</v>
       </c>
       <c r="E22">
-        <v>-35.20086076616604</v>
+        <v>-41.54110250448418</v>
       </c>
       <c r="F22">
-        <v>-2.934409663291879</v>
+        <v>-5.041174941279389</v>
       </c>
       <c r="G22">
-        <v>-11.24094552306812</v>
+        <v>-16.76733309089821</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.127342925873051</v>
       </c>
       <c r="E23">
-        <v>-35.65807135163946</v>
+        <v>-42.50232771853731</v>
       </c>
       <c r="F23">
-        <v>-2.771384473318728</v>
+        <v>-4.510496275289136</v>
       </c>
       <c r="G23">
-        <v>-11.10692074725104</v>
+        <v>-17.11756083648865</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.805529648837709</v>
       </c>
       <c r="E24">
-        <v>-36.58707194465401</v>
+        <v>-41.66351394962252</v>
       </c>
       <c r="F24">
-        <v>-2.688359693638342</v>
+        <v>-4.912018380937099</v>
       </c>
       <c r="G24">
-        <v>-10.61251284511703</v>
+        <v>-16.92082699483825</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.508857782299212</v>
       </c>
       <c r="E25">
-        <v>-36.57563528354764</v>
+        <v>-42.54274887752977</v>
       </c>
       <c r="F25">
-        <v>-2.458132369745679</v>
+        <v>-4.765335223086376</v>
       </c>
       <c r="G25">
-        <v>-10.91853597385864</v>
+        <v>-16.98437769400157</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.241214327188031</v>
       </c>
       <c r="E26">
-        <v>-36.55242685425833</v>
+        <v>-43.09664238306696</v>
       </c>
       <c r="F26">
-        <v>-2.714204756605687</v>
+        <v>-4.687286446394607</v>
       </c>
       <c r="G26">
-        <v>-10.82878472054315</v>
+        <v>-16.63969193162502</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.002887331522907</v>
       </c>
       <c r="E27">
-        <v>-36.46626810778839</v>
+        <v>-41.11027254434244</v>
       </c>
       <c r="F27">
-        <v>-2.437009000974291</v>
+        <v>-4.524776500945997</v>
       </c>
       <c r="G27">
-        <v>-10.41556080223292</v>
+        <v>-16.68978470056229</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.792291113111917</v>
       </c>
       <c r="E28">
-        <v>-36.57746478704674</v>
+        <v>-42.8921523465396</v>
       </c>
       <c r="F28">
-        <v>-2.41903591343575</v>
+        <v>-4.537839026520742</v>
       </c>
       <c r="G28">
-        <v>-10.79570344478083</v>
+        <v>-16.66469648051877</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.61527455388261</v>
       </c>
       <c r="E29">
-        <v>-36.6435103162116</v>
+        <v>-42.58089447833338</v>
       </c>
       <c r="F29">
-        <v>-2.698901497206369</v>
+        <v>-4.665342993894448</v>
       </c>
       <c r="G29">
-        <v>-10.86952436742522</v>
+        <v>-17.54378167339584</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.476802275778148</v>
       </c>
       <c r="E30">
-        <v>-36.79952983119787</v>
+        <v>-41.94706434961279</v>
       </c>
       <c r="F30">
-        <v>-2.558799718370888</v>
+        <v>-4.525838467956386</v>
       </c>
       <c r="G30">
-        <v>-11.21932555421294</v>
+        <v>-17.35143318435964</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.377554157231474</v>
       </c>
       <c r="E31">
-        <v>-36.60704025079083</v>
+        <v>-41.89642016054802</v>
       </c>
       <c r="F31">
-        <v>-2.625614176345891</v>
+        <v>-4.42845973792029</v>
       </c>
       <c r="G31">
-        <v>-11.19304953196491</v>
+        <v>-17.93865700074566</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.313641551631629</v>
       </c>
       <c r="E32">
-        <v>-35.81663813325504</v>
+        <v>-42.00883047084042</v>
       </c>
       <c r="F32">
-        <v>-2.414238837806138</v>
+        <v>-4.777880019034372</v>
       </c>
       <c r="G32">
-        <v>-10.98006544054135</v>
+        <v>-16.66863722761166</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.28599262607542</v>
       </c>
       <c r="E33">
-        <v>-35.79753250141668</v>
+        <v>-42.58195414125117</v>
       </c>
       <c r="F33">
-        <v>-2.60201316067273</v>
+        <v>-4.487615110889008</v>
       </c>
       <c r="G33">
-        <v>-11.06692265644141</v>
+        <v>-17.36276652362596</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.292130803353619</v>
       </c>
       <c r="E34">
-        <v>-35.6925103964678</v>
+        <v>-40.72867615361208</v>
       </c>
       <c r="F34">
-        <v>-2.61656840430732</v>
+        <v>-4.891221388922414</v>
       </c>
       <c r="G34">
-        <v>-11.33634375868742</v>
+        <v>-17.85066448218603</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.326655872045259</v>
       </c>
       <c r="E35">
-        <v>-34.79396152691783</v>
+        <v>-41.12959101445916</v>
       </c>
       <c r="F35">
-        <v>-2.6255578473625</v>
+        <v>-4.951214241335363</v>
       </c>
       <c r="G35">
-        <v>-11.50786305326427</v>
+        <v>-17.71473659786447</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.382236781185075</v>
       </c>
       <c r="E36">
-        <v>-34.58469395031237</v>
+        <v>-40.00117906851685</v>
       </c>
       <c r="F36">
-        <v>-2.417843892743122</v>
+        <v>-4.606195076232354</v>
       </c>
       <c r="G36">
-        <v>-11.78755437899134</v>
+        <v>-17.89413738662711</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.459864203474823</v>
       </c>
       <c r="E37">
-        <v>-34.32710302757106</v>
+        <v>-40.5830992996875</v>
       </c>
       <c r="F37">
-        <v>-2.512923074869046</v>
+        <v>-4.634225372408284</v>
       </c>
       <c r="G37">
-        <v>-11.68110498915983</v>
+        <v>-17.69381881042301</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.559986137482462</v>
       </c>
       <c r="E38">
-        <v>-33.77651983653348</v>
+        <v>-40.40139201589272</v>
       </c>
       <c r="F38">
-        <v>-2.316773957560151</v>
+        <v>-4.744389953306591</v>
       </c>
       <c r="G38">
-        <v>-11.58334099279618</v>
+        <v>-17.61439028013353</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.68235060465281</v>
       </c>
       <c r="E39">
-        <v>-33.17701554079103</v>
+        <v>-38.91379283284702</v>
       </c>
       <c r="F39">
-        <v>-2.55665507516504</v>
+        <v>-5.148073269508457</v>
       </c>
       <c r="G39">
-        <v>-12.02224046980906</v>
+        <v>-17.93619772518685</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.826131136052517</v>
       </c>
       <c r="E40">
-        <v>-32.96834119428058</v>
+        <v>-38.96891115423139</v>
       </c>
       <c r="F40">
-        <v>-2.392147935908281</v>
+        <v>-4.685676100163565</v>
       </c>
       <c r="G40">
-        <v>-12.09068675153908</v>
+        <v>-18.05128985260594</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.998654160723403</v>
       </c>
       <c r="E41">
-        <v>-32.31079544718182</v>
+        <v>-38.4495608484247</v>
       </c>
       <c r="F41">
-        <v>-2.217258039624832</v>
+        <v>-4.315916085841144</v>
       </c>
       <c r="G41">
-        <v>-12.2267065100643</v>
+        <v>-18.24956750900006</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.204841359488117</v>
       </c>
       <c r="E42">
-        <v>-31.7845120476694</v>
+        <v>-38.92138708375789</v>
       </c>
       <c r="F42">
-        <v>-2.442444747871461</v>
+        <v>-4.609732205042309</v>
       </c>
       <c r="G42">
-        <v>-12.2052177900715</v>
+        <v>-18.20107597618381</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.445869123984944</v>
       </c>
       <c r="E43">
-        <v>-31.42929175379673</v>
+        <v>-38.27912267219801</v>
       </c>
       <c r="F43">
-        <v>-2.504322136125779</v>
+        <v>-4.519342410783632</v>
       </c>
       <c r="G43">
-        <v>-12.49655745233459</v>
+        <v>-18.63109810826762</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.721166231831596</v>
       </c>
       <c r="E44">
-        <v>-30.89805873219392</v>
+        <v>-38.20390698316761</v>
       </c>
       <c r="F44">
-        <v>-2.219265173841816</v>
+        <v>-4.521811774011377</v>
       </c>
       <c r="G44">
-        <v>-12.73058729884043</v>
+        <v>-18.50777503656667</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.035792528299057</v>
       </c>
       <c r="E45">
-        <v>-30.53738389137901</v>
+        <v>-37.3983186280471</v>
       </c>
       <c r="F45">
-        <v>-2.193599038233476</v>
+        <v>-4.622509772230491</v>
       </c>
       <c r="G45">
-        <v>-12.59777329377878</v>
+        <v>-18.03909683329104</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.389676032768732</v>
       </c>
       <c r="E46">
-        <v>-29.65107322283477</v>
+        <v>-36.58001658215006</v>
       </c>
       <c r="F46">
-        <v>-2.244642209226579</v>
+        <v>-4.391851697288371</v>
       </c>
       <c r="G46">
-        <v>-12.53522992963421</v>
+        <v>-18.47569125215842</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.776212563225699</v>
       </c>
       <c r="E47">
-        <v>-29.40758623239035</v>
+        <v>-36.78098120166246</v>
       </c>
       <c r="F47">
-        <v>-2.212610070127724</v>
+        <v>-4.763401813568242</v>
       </c>
       <c r="G47">
-        <v>-12.99178565985846</v>
+        <v>-18.57541249718228</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.189047527063599</v>
       </c>
       <c r="E48">
-        <v>-28.53584592896579</v>
+        <v>-36.62875654789461</v>
       </c>
       <c r="F48">
-        <v>-2.090532737609759</v>
+        <v>-4.467822100166517</v>
       </c>
       <c r="G48">
-        <v>-12.83746980991778</v>
+        <v>-18.84482703698517</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.62734767919267</v>
       </c>
       <c r="E49">
-        <v>-28.56067555194985</v>
+        <v>-35.99937338064956</v>
       </c>
       <c r="F49">
-        <v>-2.080695874701514</v>
+        <v>-4.565355734906936</v>
       </c>
       <c r="G49">
-        <v>-12.95989218630066</v>
+        <v>-18.61786822293994</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.085641609471338</v>
       </c>
       <c r="E50">
-        <v>-27.83121990184629</v>
+        <v>-35.50137482978905</v>
       </c>
       <c r="F50">
-        <v>-1.89925607736413</v>
+        <v>-4.091900689102073</v>
       </c>
       <c r="G50">
-        <v>-12.84152211854369</v>
+        <v>-18.77156556261667</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.551362581247367</v>
       </c>
       <c r="E51">
-        <v>-27.63363352394362</v>
+        <v>-34.0834122557963</v>
       </c>
       <c r="F51">
-        <v>-2.103845430140149</v>
+        <v>-4.384596855574653</v>
       </c>
       <c r="G51">
-        <v>-13.79754867576818</v>
+        <v>-18.5247307489751</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.01711679848358</v>
       </c>
       <c r="E52">
-        <v>-26.74310911033524</v>
+        <v>-35.40485267055256</v>
       </c>
       <c r="F52">
-        <v>-2.099905714772435</v>
+        <v>-4.154619698637635</v>
       </c>
       <c r="G52">
-        <v>-13.75024986698879</v>
+        <v>-19.18258121881739</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.4798228951803</v>
       </c>
       <c r="E53">
-        <v>-26.49917832943807</v>
+        <v>-34.50112322673782</v>
       </c>
       <c r="F53">
-        <v>-2.07283549641635</v>
+        <v>-4.537857250603603</v>
       </c>
       <c r="G53">
-        <v>-13.76874283169782</v>
+        <v>-18.91867256879125</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.932373213319531</v>
       </c>
       <c r="E54">
-        <v>-26.42518759262675</v>
+        <v>-33.65354912485519</v>
       </c>
       <c r="F54">
-        <v>-1.985443563788405</v>
+        <v>-4.544957187612998</v>
       </c>
       <c r="G54">
-        <v>-13.5452785186134</v>
+        <v>-19.25866290311624</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.359624533354632</v>
       </c>
       <c r="E55">
-        <v>-25.70451265362406</v>
+        <v>-34.05699540267255</v>
       </c>
       <c r="F55">
-        <v>-2.258608483637778</v>
+        <v>-4.382644393606255</v>
       </c>
       <c r="G55">
-        <v>-13.85913720443896</v>
+        <v>-19.39461539659949</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.756876500749678</v>
       </c>
       <c r="E56">
-        <v>-25.38936256200826</v>
+        <v>-33.96706670159123</v>
       </c>
       <c r="F56">
-        <v>-2.130064086806156</v>
+        <v>-4.566006831685536</v>
       </c>
       <c r="G56">
-        <v>-14.03172617724419</v>
+        <v>-18.44642767768051</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.122546311924818</v>
       </c>
       <c r="E57">
-        <v>-24.7866588993794</v>
+        <v>-33.07796649305826</v>
       </c>
       <c r="F57">
-        <v>-2.156294340615803</v>
+        <v>-4.34363160240401</v>
       </c>
       <c r="G57">
-        <v>-13.93116493950111</v>
+        <v>-19.24281952481645</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.452400437522876</v>
       </c>
       <c r="E58">
-        <v>-24.80042093188871</v>
+        <v>-32.68256278507852</v>
       </c>
       <c r="F58">
-        <v>-2.090806098852682</v>
+        <v>-4.277339844260173</v>
       </c>
       <c r="G58">
-        <v>-13.93308609472417</v>
+        <v>-19.87725027577821</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.733713337246174</v>
       </c>
       <c r="E59">
-        <v>-24.39449305031514</v>
+        <v>-32.49264084943383</v>
       </c>
       <c r="F59">
-        <v>-2.162348877962864</v>
+        <v>-4.326826512903416</v>
       </c>
       <c r="G59">
-        <v>-14.22412388460379</v>
+        <v>-19.81085475752285</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.96879931428697</v>
       </c>
       <c r="E60">
-        <v>-23.84490838779625</v>
+        <v>-32.32491975761175</v>
       </c>
       <c r="F60">
-        <v>-2.030743663577899</v>
+        <v>-4.641937472928348</v>
       </c>
       <c r="G60">
-        <v>-14.28251650347567</v>
+        <v>-18.23174227287838</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.16004830331559</v>
       </c>
       <c r="E61">
-        <v>-23.87889005674981</v>
+        <v>-33.1573981913898</v>
       </c>
       <c r="F61">
-        <v>-2.26350330662092</v>
+        <v>-4.71297411955542</v>
       </c>
       <c r="G61">
-        <v>-14.54990652957638</v>
+        <v>-18.78745979985062</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.30668946320481</v>
       </c>
       <c r="E62">
-        <v>-23.01115745282204</v>
+        <v>-32.02289091943317</v>
       </c>
       <c r="F62">
-        <v>-2.245010004353421</v>
+        <v>-4.627888361776868</v>
       </c>
       <c r="G62">
-        <v>-14.86039211963884</v>
+        <v>-19.6429759782662</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.39989767427579</v>
       </c>
       <c r="E63">
-        <v>-23.77194108611066</v>
+        <v>-31.3706525438714</v>
       </c>
       <c r="F63">
-        <v>-2.397688885465607</v>
+        <v>-4.448500430496218</v>
       </c>
       <c r="G63">
-        <v>-14.74658951229262</v>
+        <v>-20.33400287929603</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.44718924345821</v>
       </c>
       <c r="E64">
-        <v>-23.15220130426494</v>
+        <v>-31.01185249129567</v>
       </c>
       <c r="F64">
-        <v>-2.240724859778739</v>
+        <v>-4.547960847815549</v>
       </c>
       <c r="G64">
-        <v>-15.18012419205581</v>
+        <v>-19.68867519153536</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.45399881554203</v>
       </c>
       <c r="E65">
-        <v>-22.69693569837781</v>
+        <v>-31.36441230668883</v>
       </c>
       <c r="F65">
-        <v>-2.52307057555334</v>
+        <v>-4.664701837524681</v>
       </c>
       <c r="G65">
-        <v>-14.49749885882893</v>
+        <v>-19.35038945181051</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.42149921959299</v>
       </c>
       <c r="E66">
-        <v>-22.5828090964365</v>
+        <v>-30.97197248494712</v>
       </c>
       <c r="F66">
-        <v>-2.393402084156119</v>
+        <v>-4.784438203762336</v>
       </c>
       <c r="G66">
-        <v>-14.80754476520242</v>
+        <v>-19.65007654172084</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.34396075305052</v>
       </c>
       <c r="E67">
-        <v>-22.56376233476024</v>
+        <v>-30.9312230115891</v>
       </c>
       <c r="F67">
-        <v>-2.578158664574313</v>
+        <v>-4.683055145701107</v>
       </c>
       <c r="G67">
-        <v>-14.71083240034857</v>
+        <v>-19.90754907565812</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.23153907065889</v>
       </c>
       <c r="E68">
-        <v>-22.41801792729738</v>
+        <v>-31.91493662756432</v>
       </c>
       <c r="F68">
-        <v>-2.688354723433925</v>
+        <v>-4.459756286765458</v>
       </c>
       <c r="G68">
-        <v>-15.0083259936464</v>
+        <v>-19.68073791658307</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.09017090153123</v>
       </c>
       <c r="E69">
-        <v>-21.46996830836957</v>
+        <v>-30.8662801658451</v>
       </c>
       <c r="F69">
-        <v>-2.732477713144041</v>
+        <v>-4.74615354750715</v>
       </c>
       <c r="G69">
-        <v>-15.08904896584108</v>
+        <v>-19.43518277934968</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.920812427961565</v>
       </c>
       <c r="E70">
-        <v>-22.05530527317901</v>
+        <v>-30.76690053950977</v>
       </c>
       <c r="F70">
-        <v>-2.812057312796184</v>
+        <v>-4.790933432567686</v>
       </c>
       <c r="G70">
-        <v>-14.49595012225287</v>
+        <v>-19.68149095693096</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.718915812565255</v>
       </c>
       <c r="E71">
-        <v>-21.93046883020956</v>
+        <v>-30.62097046461259</v>
       </c>
       <c r="F71">
-        <v>-2.822425987577025</v>
+        <v>-4.89661737418425</v>
       </c>
       <c r="G71">
-        <v>-14.62883959541038</v>
+        <v>-19.47125160734188</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.496166930465428</v>
       </c>
       <c r="E72">
-        <v>-22.09858842774432</v>
+        <v>-31.32858528457715</v>
       </c>
       <c r="F72">
-        <v>-2.947829215217231</v>
+        <v>-5.189938129678541</v>
       </c>
       <c r="G72">
-        <v>-14.54407908008681</v>
+        <v>-19.04755238920312</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.258023507704271</v>
       </c>
       <c r="E73">
-        <v>-22.56505747832643</v>
+        <v>-31.05323821525177</v>
       </c>
       <c r="F73">
-        <v>-2.963150698699411</v>
+        <v>-4.961536527541647</v>
       </c>
       <c r="G73">
-        <v>-14.30509458902621</v>
+        <v>-19.19258566335214</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.005286350873577</v>
       </c>
       <c r="E74">
-        <v>-22.45617937776002</v>
+        <v>-32.0578009255583</v>
       </c>
       <c r="F74">
-        <v>-3.094923243299742</v>
+        <v>-5.064003090165738</v>
       </c>
       <c r="G74">
-        <v>-14.66538584113948</v>
+        <v>-19.4232719450889</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.734572735031106</v>
       </c>
       <c r="E75">
-        <v>-22.82889995943533</v>
+        <v>-30.80900855507009</v>
       </c>
       <c r="F75">
-        <v>-3.156996954628523</v>
+        <v>-4.954365350935612</v>
       </c>
       <c r="G75">
-        <v>-14.20278610080272</v>
+        <v>-18.70346544976117</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.4581277770146</v>
       </c>
       <c r="E76">
-        <v>-23.40681475534621</v>
+        <v>-31.64283194562842</v>
       </c>
       <c r="F76">
-        <v>-3.103091774258748</v>
+        <v>-5.238867307059699</v>
       </c>
       <c r="G76">
-        <v>-13.78764923032334</v>
+        <v>-18.79590402353385</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.179536242956036</v>
       </c>
       <c r="E77">
-        <v>-23.17404666287794</v>
+        <v>-32.52677195802965</v>
       </c>
       <c r="F77">
-        <v>-3.214679490355064</v>
+        <v>-4.974310781260218</v>
       </c>
       <c r="G77">
-        <v>-13.78571166899249</v>
+        <v>-19.32022846323609</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.898186942537966</v>
       </c>
       <c r="E78">
-        <v>-23.41980694727421</v>
+        <v>-30.86370799260874</v>
       </c>
       <c r="F78">
-        <v>-3.238009629887509</v>
+        <v>-5.300396781004841</v>
       </c>
       <c r="G78">
-        <v>-13.76211476414774</v>
+        <v>-18.44663931647109</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.610842375384226</v>
       </c>
       <c r="E79">
-        <v>-23.86273698996445</v>
+        <v>-32.891837154395</v>
       </c>
       <c r="F79">
-        <v>-3.492414513165682</v>
+        <v>-5.184976208935772</v>
       </c>
       <c r="G79">
-        <v>-13.06736531725871</v>
+        <v>-18.17677853053612</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.329649922886599</v>
       </c>
       <c r="E80">
-        <v>-23.96527975539414</v>
+        <v>-32.09773527359494</v>
       </c>
       <c r="F80">
-        <v>-3.293238541366958</v>
+        <v>-5.290494477071776</v>
       </c>
       <c r="G80">
-        <v>-12.92448780567425</v>
+        <v>-19.03685560691933</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.057144204284524</v>
       </c>
       <c r="E81">
-        <v>-24.84012206351395</v>
+        <v>-33.21665327378017</v>
       </c>
       <c r="F81">
-        <v>-3.351032078325474</v>
+        <v>-5.356125198028178</v>
       </c>
       <c r="G81">
-        <v>-13.02572005322624</v>
+        <v>-17.88722221219058</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.792016997243094</v>
       </c>
       <c r="E82">
-        <v>-24.87544868924779</v>
+        <v>-33.43089990755706</v>
       </c>
       <c r="F82">
-        <v>-3.449423901695194</v>
+        <v>-5.53551975624805</v>
       </c>
       <c r="G82">
-        <v>-12.50125616160772</v>
+        <v>-17.81213965985659</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.533504721990296</v>
       </c>
       <c r="E83">
-        <v>-25.4817796595568</v>
+        <v>-34.00732936399343</v>
       </c>
       <c r="F83">
-        <v>-3.487505607936692</v>
+        <v>-5.487450424230998</v>
       </c>
       <c r="G83">
-        <v>-12.23232396137407</v>
+        <v>-17.56626460352116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.292632629139982</v>
       </c>
       <c r="E84">
-        <v>-26.1689937041168</v>
+        <v>-34.8871688431807</v>
       </c>
       <c r="F84">
-        <v>-3.509873184547085</v>
+        <v>-5.261426236540139</v>
       </c>
       <c r="G84">
-        <v>-12.05053444331615</v>
+        <v>-16.80117232884076</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.071784233439247</v>
       </c>
       <c r="E85">
-        <v>-27.57014884683009</v>
+        <v>-36.12935869856573</v>
       </c>
       <c r="F85">
-        <v>-3.509725735149386</v>
+        <v>-5.666560024064307</v>
       </c>
       <c r="G85">
-        <v>-11.7298540978685</v>
+        <v>-16.69842251631752</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.86888204457151</v>
       </c>
       <c r="E86">
-        <v>-28.00276755420486</v>
+        <v>-35.57224091953508</v>
       </c>
       <c r="F86">
-        <v>-3.721280001048143</v>
+        <v>-5.540875979874552</v>
       </c>
       <c r="G86">
-        <v>-11.5434675884058</v>
+        <v>-16.71622314327751</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.68597972508158</v>
       </c>
       <c r="E87">
-        <v>-29.12745483027586</v>
+        <v>-36.90773545337415</v>
       </c>
       <c r="F87">
-        <v>-3.552243348832877</v>
+        <v>-5.6984853037682</v>
       </c>
       <c r="G87">
-        <v>-11.64765293536129</v>
+        <v>-17.54128958562145</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.532011516652813</v>
       </c>
       <c r="E88">
-        <v>-29.58109471399424</v>
+        <v>-38.15535042062037</v>
       </c>
       <c r="F88">
-        <v>-3.645208537346857</v>
+        <v>-5.550004588653402</v>
       </c>
       <c r="G88">
-        <v>-11.29608973259615</v>
+        <v>-16.63311800423068</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.408636379221069</v>
       </c>
       <c r="E89">
-        <v>-31.28998910060978</v>
+        <v>-38.76387543658609</v>
       </c>
       <c r="F89">
-        <v>-3.702992133896539</v>
+        <v>-5.510455015374142</v>
       </c>
       <c r="G89">
-        <v>-11.1735590759018</v>
+        <v>-16.68660191564963</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.311258619698293</v>
       </c>
       <c r="E90">
-        <v>-31.99676388864592</v>
+        <v>-40.94493116561138</v>
       </c>
       <c r="F90">
-        <v>-3.790976349217486</v>
+        <v>-5.854061814055378</v>
       </c>
       <c r="G90">
-        <v>-10.6877512554751</v>
+        <v>-16.57231040629105</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.241550115491673</v>
       </c>
       <c r="E91">
-        <v>-33.28891413352057</v>
+        <v>-41.07089293437173</v>
       </c>
       <c r="F91">
-        <v>-3.761750718879316</v>
+        <v>-6.236511588621284</v>
       </c>
       <c r="G91">
-        <v>-11.13175303201292</v>
+        <v>-16.81437596439596</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.202898036943264</v>
       </c>
       <c r="E92">
-        <v>-34.71453209282329</v>
+        <v>-41.53976660465192</v>
       </c>
       <c r="F92">
-        <v>-3.793624639804236</v>
+        <v>-6.00478988993397</v>
       </c>
       <c r="G92">
-        <v>-11.13723923446031</v>
+        <v>-16.40054502009724</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.192926869563799</v>
       </c>
       <c r="E93">
-        <v>-36.28835568521204</v>
+        <v>-42.75338631752255</v>
       </c>
       <c r="F93">
-        <v>-3.90478574668811</v>
+        <v>-6.237409538885919</v>
       </c>
       <c r="G93">
-        <v>-11.10591341223229</v>
+        <v>-16.39727528281325</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.202265019703233</v>
       </c>
       <c r="E94">
-        <v>-37.89417068222798</v>
+        <v>-44.34496832073238</v>
       </c>
       <c r="F94">
-        <v>-4.152528899312969</v>
+        <v>-6.151921194549607</v>
       </c>
       <c r="G94">
-        <v>-11.41998865868078</v>
+        <v>-17.09820491050949</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.230569715071276</v>
       </c>
       <c r="E95">
-        <v>-38.87784580617414</v>
+        <v>-46.14383442893232</v>
       </c>
       <c r="F95">
-        <v>-4.081766442296224</v>
+        <v>-6.385156320481836</v>
       </c>
       <c r="G95">
-        <v>-11.3909170356641</v>
+        <v>-16.91176426089106</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.277850555111527</v>
       </c>
       <c r="E96">
-        <v>-40.8324189646538</v>
+        <v>-47.4940397105853</v>
       </c>
       <c r="F96">
-        <v>-4.043453621549344</v>
+        <v>-6.508943817502881</v>
       </c>
       <c r="G96">
-        <v>-11.62751607865098</v>
+        <v>-17.37093020286586</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.337197228921696</v>
       </c>
       <c r="E97">
-        <v>-42.43804376576142</v>
+        <v>-48.27710796446566</v>
       </c>
       <c r="F97">
-        <v>-4.000911985211173</v>
+        <v>-6.35673047887107</v>
       </c>
       <c r="G97">
-        <v>-12.06643852421478</v>
+        <v>-17.49410069776429</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.402284758216092</v>
       </c>
       <c r="E98">
-        <v>-44.00297117096211</v>
+        <v>-49.72846350579098</v>
       </c>
       <c r="F98">
-        <v>-4.066300822885958</v>
+        <v>-6.28698442865756</v>
       </c>
       <c r="G98">
-        <v>-11.95808930710036</v>
+        <v>-16.66390078429061</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.468644692914584</v>
       </c>
       <c r="E99">
-        <v>-46.13292080657383</v>
+        <v>-50.9906035534168</v>
       </c>
       <c r="F99">
-        <v>-4.183420376498169</v>
+        <v>-6.557513069247523</v>
       </c>
       <c r="G99">
-        <v>-12.15471322782852</v>
+        <v>-17.72149755488771</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.544126518157261</v>
       </c>
       <c r="E100">
-        <v>-48.09751774226947</v>
+        <v>-51.1919247902573</v>
       </c>
       <c r="F100">
-        <v>-4.307476678741422</v>
+        <v>-6.76201295834404</v>
       </c>
       <c r="G100">
-        <v>-12.43196988715848</v>
+        <v>-18.89549073847378</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.613483870893394</v>
       </c>
       <c r="E101">
-        <v>-49.72308254655137</v>
+        <v>-52.77509854935339</v>
       </c>
       <c r="F101">
-        <v>-4.341051237944288</v>
+        <v>-6.795279779056767</v>
       </c>
       <c r="G101">
-        <v>-12.77066413896748</v>
+        <v>-18.24303295626443</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.694122337633847</v>
       </c>
       <c r="E102">
-        <v>-51.48761150058814</v>
+        <v>-54.6181750171717</v>
       </c>
       <c r="F102">
-        <v>-4.349213141964072</v>
+        <v>-6.652297766761753</v>
       </c>
       <c r="G102">
-        <v>-13.21239859140773</v>
+        <v>-19.08625439749677</v>
       </c>
     </row>
   </sheetData>
